--- a/new_leave.xlsx
+++ b/new_leave.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3027" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="68">
   <si>
     <t>Yes</t>
   </si>
@@ -229,12 +229,15 @@
   <si>
     <t>end_date</t>
   </si>
+  <si>
+    <t>requested_days</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +274,12 @@
     <font>
       <sz val="7"/>
       <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFE394DC"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -311,7 +320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -333,6 +342,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -617,16 +629,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G605"/>
+  <dimension ref="A1:H605"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.90625" customWidth="1"/>
     <col min="2" max="2" width="23.26953125" customWidth="1"/>
     <col min="3" max="4" width="13.81640625" customWidth="1"/>
     <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -648,8 +661,11 @@
       <c r="G1" s="10" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H1" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -671,8 +687,11 @@
       <c r="G2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>52</v>
       </c>
@@ -694,8 +713,11 @@
       <c r="G3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -717,8 +739,11 @@
       <c r="G4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -740,8 +765,11 @@
       <c r="G5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
@@ -763,8 +791,11 @@
       <c r="G6" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -786,8 +817,11 @@
       <c r="G7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -809,8 +843,11 @@
       <c r="G8" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -832,8 +869,11 @@
       <c r="G9" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -855,8 +895,11 @@
       <c r="G10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -878,8 +921,11 @@
       <c r="G11" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -901,8 +947,11 @@
       <c r="G12" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -924,8 +973,11 @@
       <c r="G13" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>58</v>
       </c>
@@ -947,8 +999,11 @@
       <c r="G14" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -970,8 +1025,11 @@
       <c r="G15" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>34</v>
       </c>
@@ -993,9 +1051,12 @@
       <c r="G16" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1016,8 +1077,11 @@
       <c r="G17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>19</v>
       </c>
@@ -1039,8 +1103,11 @@
       <c r="G18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1062,8 +1129,11 @@
       <c r="G19" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1085,8 +1155,11 @@
       <c r="G20" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1108,8 +1181,11 @@
       <c r="G21" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>52</v>
       </c>
@@ -1131,8 +1207,11 @@
       <c r="G22" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1154,8 +1233,11 @@
       <c r="G23" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1177,8 +1259,11 @@
       <c r="G24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>26</v>
       </c>
@@ -1200,8 +1285,11 @@
       <c r="G25" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -1223,8 +1311,11 @@
       <c r="G26" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -1246,8 +1337,11 @@
       <c r="G27" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -1269,8 +1363,11 @@
       <c r="G28" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1292,8 +1389,11 @@
       <c r="G29" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1315,8 +1415,11 @@
       <c r="G30" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1338,8 +1441,11 @@
       <c r="G31" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>47</v>
       </c>
@@ -1361,8 +1467,11 @@
       <c r="G32" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -1384,8 +1493,11 @@
       <c r="G33" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>44</v>
       </c>
@@ -1407,8 +1519,11 @@
       <c r="G34" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -1430,8 +1545,11 @@
       <c r="G35" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -1453,8 +1571,11 @@
       <c r="G36" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>58</v>
       </c>
@@ -1476,8 +1597,11 @@
       <c r="G37" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -1499,8 +1623,11 @@
       <c r="G38" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>34</v>
       </c>
@@ -1522,8 +1649,11 @@
       <c r="G39" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>19</v>
       </c>
@@ -1545,8 +1675,11 @@
       <c r="G40" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -1568,8 +1701,11 @@
       <c r="G41" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>30</v>
       </c>
@@ -1591,8 +1727,11 @@
       <c r="G42" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -1614,8 +1753,11 @@
       <c r="G43" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>52</v>
       </c>
@@ -1637,8 +1779,11 @@
       <c r="G44" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -1660,8 +1805,11 @@
       <c r="G45" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1683,8 +1831,11 @@
       <c r="G46" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>26</v>
       </c>
@@ -1706,8 +1857,11 @@
       <c r="G47" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>45</v>
       </c>
@@ -1729,8 +1883,11 @@
       <c r="G48" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -1752,8 +1909,11 @@
       <c r="G49" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -1775,8 +1935,11 @@
       <c r="G50" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -1798,8 +1961,11 @@
       <c r="G51" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -1821,8 +1987,11 @@
       <c r="G52" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -1844,8 +2013,11 @@
       <c r="G53" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -1867,8 +2039,11 @@
       <c r="G54" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>58</v>
       </c>
@@ -1890,8 +2065,11 @@
       <c r="G55" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -1913,8 +2091,11 @@
       <c r="G56" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>43</v>
       </c>
@@ -1936,8 +2117,11 @@
       <c r="G57" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>38</v>
       </c>
@@ -1959,8 +2143,11 @@
       <c r="G58" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -1982,8 +2169,11 @@
       <c r="G59" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>45</v>
       </c>
@@ -2005,8 +2195,11 @@
       <c r="G60" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -2028,8 +2221,11 @@
       <c r="G61" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>43</v>
       </c>
@@ -2051,8 +2247,11 @@
       <c r="G62" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -2074,8 +2273,11 @@
       <c r="G63" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>56</v>
       </c>
@@ -2097,8 +2299,11 @@
       <c r="G64" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>26</v>
       </c>
@@ -2120,8 +2325,11 @@
       <c r="G65" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>41</v>
       </c>
@@ -2143,8 +2351,11 @@
       <c r="G66" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>45</v>
       </c>
@@ -2166,8 +2377,11 @@
       <c r="G67" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -2189,8 +2403,11 @@
       <c r="G68" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>54</v>
       </c>
@@ -2212,8 +2429,11 @@
       <c r="G69" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -2235,8 +2455,11 @@
       <c r="G70" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -2258,8 +2481,11 @@
       <c r="G71" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -2281,8 +2507,11 @@
       <c r="G72" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>58</v>
       </c>
@@ -2304,8 +2533,11 @@
       <c r="G73" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -2327,8 +2559,11 @@
       <c r="G74" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>56</v>
       </c>
@@ -2350,8 +2585,11 @@
       <c r="G75" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -2373,8 +2611,11 @@
       <c r="G76" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>26</v>
       </c>
@@ -2396,8 +2637,11 @@
       <c r="G77" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>41</v>
       </c>
@@ -2419,8 +2663,11 @@
       <c r="G78" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>45</v>
       </c>
@@ -2442,8 +2689,11 @@
       <c r="G79" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -2465,8 +2715,11 @@
       <c r="G80" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -2488,8 +2741,11 @@
       <c r="G81" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -2511,8 +2767,11 @@
       <c r="G82" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>27</v>
       </c>
@@ -2534,8 +2793,11 @@
       <c r="G83" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -2557,8 +2819,11 @@
       <c r="G84" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -2580,8 +2845,11 @@
       <c r="G85" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="8" t="s">
         <v>58</v>
       </c>
@@ -2603,8 +2871,11 @@
       <c r="G86" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>35</v>
       </c>
@@ -2626,8 +2897,11 @@
       <c r="G87" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -2649,8 +2923,11 @@
       <c r="G88" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>45</v>
       </c>
@@ -2672,8 +2949,11 @@
       <c r="G89" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>28</v>
       </c>
@@ -2695,8 +2975,11 @@
       <c r="G90" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>54</v>
       </c>
@@ -2718,8 +3001,11 @@
       <c r="G91" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -2741,8 +3027,11 @@
       <c r="G92" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>37</v>
       </c>
@@ -2764,8 +3053,11 @@
       <c r="G93" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -2787,8 +3079,11 @@
       <c r="G94" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
         <v>58</v>
       </c>
@@ -2810,8 +3105,11 @@
       <c r="G95" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>21</v>
       </c>
@@ -2833,8 +3131,11 @@
       <c r="G96" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -2856,8 +3157,11 @@
       <c r="G97" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>45</v>
       </c>
@@ -2879,8 +3183,11 @@
       <c r="G98" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>54</v>
       </c>
@@ -2902,8 +3209,11 @@
       <c r="G99" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>39</v>
       </c>
@@ -2925,8 +3235,11 @@
       <c r="G100" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -2948,8 +3261,11 @@
       <c r="G101" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="8" t="s">
         <v>58</v>
       </c>
@@ -2971,8 +3287,11 @@
       <c r="G102" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -2994,8 +3313,11 @@
       <c r="G103" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>45</v>
       </c>
@@ -3017,8 +3339,11 @@
       <c r="G104" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>54</v>
       </c>
@@ -3040,8 +3365,11 @@
       <c r="G105" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>39</v>
       </c>
@@ -3063,8 +3391,11 @@
       <c r="G106" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -3086,8 +3417,11 @@
       <c r="G107" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
         <v>58</v>
       </c>
@@ -3109,8 +3443,11 @@
       <c r="G108" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>21</v>
       </c>
@@ -3132,8 +3469,11 @@
       <c r="G109" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>49</v>
       </c>
@@ -3155,8 +3495,11 @@
       <c r="G110" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>45</v>
       </c>
@@ -3178,8 +3521,11 @@
       <c r="G111" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -3201,8 +3547,11 @@
       <c r="G112" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>39</v>
       </c>
@@ -3224,8 +3573,11 @@
       <c r="G113" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>37</v>
       </c>
@@ -3247,8 +3599,11 @@
       <c r="G114" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>44</v>
       </c>
@@ -3270,8 +3625,11 @@
       <c r="G115" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>17</v>
       </c>
@@ -3293,8 +3651,11 @@
       <c r="G116" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="8" t="s">
         <v>58</v>
       </c>
@@ -3316,8 +3677,11 @@
       <c r="G117" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="8" t="s">
         <v>50</v>
       </c>
@@ -3339,8 +3703,11 @@
       <c r="G118" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>21</v>
       </c>
@@ -3362,8 +3729,11 @@
       <c r="G119" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>36</v>
       </c>
@@ -3385,8 +3755,11 @@
       <c r="G120" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>31</v>
       </c>
@@ -3408,8 +3781,11 @@
       <c r="G121" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>46</v>
       </c>
@@ -3431,8 +3807,11 @@
       <c r="G122" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>45</v>
       </c>
@@ -3454,8 +3833,11 @@
       <c r="G123" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -3477,8 +3859,11 @@
       <c r="G124" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>54</v>
       </c>
@@ -3500,8 +3885,11 @@
       <c r="G125" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>39</v>
       </c>
@@ -3523,8 +3911,11 @@
       <c r="G126" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>55</v>
       </c>
@@ -3546,8 +3937,11 @@
       <c r="G127" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -3569,8 +3963,11 @@
       <c r="G128" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
         <v>58</v>
       </c>
@@ -3592,8 +3989,11 @@
       <c r="G129" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
         <v>18</v>
       </c>
@@ -3615,8 +4015,11 @@
       <c r="G130" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="8" t="s">
         <v>34</v>
       </c>
@@ -3638,8 +4041,11 @@
       <c r="G131" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="8" t="s">
         <v>34</v>
       </c>
@@ -3661,8 +4067,11 @@
       <c r="G132" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>51</v>
       </c>
@@ -3684,8 +4093,11 @@
       <c r="G133" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>21</v>
       </c>
@@ -3707,8 +4119,11 @@
       <c r="G134" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="8" t="s">
         <v>48</v>
       </c>
@@ -3730,8 +4145,11 @@
       <c r="G135" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>30</v>
       </c>
@@ -3753,8 +4171,11 @@
       <c r="G136" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>36</v>
       </c>
@@ -3776,8 +4197,11 @@
       <c r="G137" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -3799,8 +4223,11 @@
       <c r="G138" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="8" t="s">
         <v>52</v>
       </c>
@@ -3822,8 +4249,11 @@
       <c r="G139" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>15</v>
       </c>
@@ -3845,8 +4275,11 @@
       <c r="G140" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>49</v>
       </c>
@@ -3868,8 +4301,11 @@
       <c r="G141" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
         <v>26</v>
       </c>
@@ -3891,8 +4327,11 @@
       <c r="G142" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>31</v>
       </c>
@@ -3914,8 +4353,11 @@
       <c r="G143" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>46</v>
       </c>
@@ -3937,8 +4379,11 @@
       <c r="G144" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>41</v>
       </c>
@@ -3960,8 +4405,11 @@
       <c r="G145" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>45</v>
       </c>
@@ -3983,8 +4431,11 @@
       <c r="G146" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -4006,8 +4457,11 @@
       <c r="G147" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>29</v>
       </c>
@@ -4029,8 +4483,11 @@
       <c r="G148" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>54</v>
       </c>
@@ -4052,8 +4509,11 @@
       <c r="G149" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>27</v>
       </c>
@@ -4075,8 +4535,11 @@
       <c r="G150" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>25</v>
       </c>
@@ -4098,8 +4561,11 @@
       <c r="G151" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>33</v>
       </c>
@@ -4121,8 +4587,11 @@
       <c r="G152" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="8" t="s">
         <v>47</v>
       </c>
@@ -4144,8 +4613,11 @@
       <c r="G153" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>39</v>
       </c>
@@ -4167,8 +4639,11 @@
       <c r="G154" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>32</v>
       </c>
@@ -4190,8 +4665,11 @@
       <c r="G155" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>37</v>
       </c>
@@ -4213,8 +4691,11 @@
       <c r="G156" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -4236,8 +4717,11 @@
       <c r="G157" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>17</v>
       </c>
@@ -4259,8 +4743,11 @@
       <c r="G158" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -4282,8 +4769,11 @@
       <c r="G159" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="8" t="s">
         <v>58</v>
       </c>
@@ -4305,8 +4795,11 @@
       <c r="G160" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="8" t="s">
         <v>53</v>
       </c>
@@ -4328,8 +4821,11 @@
       <c r="G161" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="8" t="s">
         <v>34</v>
       </c>
@@ -4351,8 +4847,11 @@
       <c r="G162" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
         <v>22</v>
       </c>
@@ -4374,8 +4873,11 @@
       <c r="G163" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>24</v>
       </c>
@@ -4397,8 +4899,11 @@
       <c r="G164" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="6" t="s">
         <v>18</v>
       </c>
@@ -4420,8 +4925,11 @@
       <c r="G165" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>23</v>
       </c>
@@ -4443,8 +4951,11 @@
       <c r="G166" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>51</v>
       </c>
@@ -4466,8 +4977,11 @@
       <c r="G167" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>21</v>
       </c>
@@ -4489,8 +5003,11 @@
       <c r="G168" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="8" t="s">
         <v>48</v>
       </c>
@@ -4512,8 +5029,11 @@
       <c r="G169" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>30</v>
       </c>
@@ -4535,8 +5055,11 @@
       <c r="G170" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>36</v>
       </c>
@@ -4558,8 +5081,11 @@
       <c r="G171" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -4581,8 +5107,11 @@
       <c r="G172" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="8" t="s">
         <v>52</v>
       </c>
@@ -4604,8 +5133,11 @@
       <c r="G173" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>15</v>
       </c>
@@ -4627,8 +5159,11 @@
       <c r="G174" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>49</v>
       </c>
@@ -4650,8 +5185,11 @@
       <c r="G175" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="8" t="s">
         <v>26</v>
       </c>
@@ -4673,8 +5211,11 @@
       <c r="G176" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>31</v>
       </c>
@@ -4696,8 +5237,11 @@
       <c r="G177" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>46</v>
       </c>
@@ -4719,8 +5263,11 @@
       <c r="G178" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>45</v>
       </c>
@@ -4742,8 +5289,11 @@
       <c r="G179" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>13</v>
       </c>
@@ -4765,8 +5315,11 @@
       <c r="G180" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>29</v>
       </c>
@@ -4788,8 +5341,11 @@
       <c r="G181" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>54</v>
       </c>
@@ -4811,8 +5367,11 @@
       <c r="G182" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>33</v>
       </c>
@@ -4834,8 +5393,11 @@
       <c r="G183" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="8" t="s">
         <v>47</v>
       </c>
@@ -4857,8 +5419,11 @@
       <c r="G184" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>39</v>
       </c>
@@ -4880,8 +5445,11 @@
       <c r="G185" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>32</v>
       </c>
@@ -4903,8 +5471,11 @@
       <c r="G186" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>42</v>
       </c>
@@ -4926,8 +5497,11 @@
       <c r="G187" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>44</v>
       </c>
@@ -4949,8 +5523,11 @@
       <c r="G188" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -4972,8 +5549,11 @@
       <c r="G189" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>35</v>
       </c>
@@ -4995,8 +5575,11 @@
       <c r="G190" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>20</v>
       </c>
@@ -5018,8 +5601,11 @@
       <c r="G191" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="8" t="s">
         <v>58</v>
       </c>
@@ -5041,8 +5627,11 @@
       <c r="G192" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="8" t="s">
         <v>53</v>
       </c>
@@ -5064,8 +5653,11 @@
       <c r="G193" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="8" t="s">
         <v>34</v>
       </c>
@@ -5087,8 +5679,11 @@
       <c r="G194" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
         <v>22</v>
       </c>
@@ -5110,8 +5705,11 @@
       <c r="G195" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7" t="s">
         <v>24</v>
       </c>
@@ -5133,8 +5731,11 @@
       <c r="G196" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197" s="6" t="s">
         <v>18</v>
       </c>
@@ -5156,8 +5757,11 @@
       <c r="G197" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="8" t="s">
         <v>50</v>
       </c>
@@ -5179,8 +5783,11 @@
       <c r="G198" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -5202,8 +5809,11 @@
       <c r="G199" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>45</v>
       </c>
@@ -5225,8 +5835,11 @@
       <c r="G200" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
         <v>22</v>
       </c>
@@ -5248,8 +5861,11 @@
       <c r="G201" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="8" t="s">
         <v>58</v>
       </c>
@@ -5271,8 +5887,11 @@
       <c r="G202" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>17</v>
       </c>
@@ -5294,8 +5913,11 @@
       <c r="G203" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -5317,8 +5939,11 @@
       <c r="G204" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>36</v>
       </c>
@@ -5340,8 +5965,11 @@
       <c r="G205" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>54</v>
       </c>
@@ -5363,8 +5991,11 @@
       <c r="G206" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>44</v>
       </c>
@@ -5386,8 +6017,11 @@
       <c r="G207" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>33</v>
       </c>
@@ -5409,8 +6043,11 @@
       <c r="G208" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>16</v>
       </c>
@@ -5432,8 +6069,11 @@
       <c r="G209" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="8" t="s">
         <v>47</v>
       </c>
@@ -5455,8 +6095,11 @@
       <c r="G210" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>21</v>
       </c>
@@ -5478,8 +6121,11 @@
       <c r="G211" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>39</v>
       </c>
@@ -5501,8 +6147,11 @@
       <c r="G212" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>15</v>
       </c>
@@ -5524,8 +6173,11 @@
       <c r="G213" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>42</v>
       </c>
@@ -5547,8 +6199,11 @@
       <c r="G214" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>32</v>
       </c>
@@ -5570,8 +6225,11 @@
       <c r="G215" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>49</v>
       </c>
@@ -5593,8 +6251,11 @@
       <c r="G216" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="8" t="s">
         <v>48</v>
       </c>
@@ -5616,8 +6277,11 @@
       <c r="G217" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="8" t="s">
         <v>34</v>
       </c>
@@ -5639,8 +6303,11 @@
       <c r="G218" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>31</v>
       </c>
@@ -5662,8 +6329,11 @@
       <c r="G219" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>23</v>
       </c>
@@ -5685,8 +6355,11 @@
       <c r="G220" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>51</v>
       </c>
@@ -5708,8 +6381,11 @@
       <c r="G221" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>21</v>
       </c>
@@ -5731,8 +6407,11 @@
       <c r="G222" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="8" t="s">
         <v>48</v>
       </c>
@@ -5754,8 +6433,11 @@
       <c r="G223" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>36</v>
       </c>
@@ -5777,8 +6459,11 @@
       <c r="G224" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -5800,8 +6485,11 @@
       <c r="G225" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>15</v>
       </c>
@@ -5823,8 +6511,11 @@
       <c r="G226" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>49</v>
       </c>
@@ -5846,8 +6537,11 @@
       <c r="G227" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="8" t="s">
         <v>26</v>
       </c>
@@ -5869,8 +6563,11 @@
       <c r="G228" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>31</v>
       </c>
@@ -5892,8 +6589,11 @@
       <c r="G229" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>45</v>
       </c>
@@ -5915,8 +6615,11 @@
       <c r="G230" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>13</v>
       </c>
@@ -5938,8 +6641,11 @@
       <c r="G231" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>54</v>
       </c>
@@ -5961,8 +6667,11 @@
       <c r="G232" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>33</v>
       </c>
@@ -5984,8 +6693,11 @@
       <c r="G233" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="8" t="s">
         <v>47</v>
       </c>
@@ -6007,8 +6719,11 @@
       <c r="G234" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>39</v>
       </c>
@@ -6030,8 +6745,11 @@
       <c r="G235" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>32</v>
       </c>
@@ -6053,8 +6771,11 @@
       <c r="G236" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>17</v>
       </c>
@@ -6076,8 +6797,11 @@
       <c r="G237" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="8" t="s">
         <v>58</v>
       </c>
@@ -6099,8 +6823,11 @@
       <c r="G238" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>10</v>
       </c>
@@ -6122,8 +6849,11 @@
       <c r="G239" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="8" t="s">
         <v>34</v>
       </c>
@@ -6145,8 +6875,11 @@
       <c r="G240" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="7" t="s">
         <v>22</v>
       </c>
@@ -6168,8 +6901,11 @@
       <c r="G241" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>41</v>
       </c>
@@ -6191,8 +6927,11 @@
       <c r="G242" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -6214,8 +6953,11 @@
       <c r="G243" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="8" t="s">
         <v>26</v>
       </c>
@@ -6237,8 +6979,11 @@
       <c r="G244" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>30</v>
       </c>
@@ -6260,8 +7005,11 @@
       <c r="G245" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>39</v>
       </c>
@@ -6283,8 +7031,11 @@
       <c r="G246" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>54</v>
       </c>
@@ -6306,8 +7057,11 @@
       <c r="G247" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>12</v>
       </c>
@@ -6329,8 +7083,11 @@
       <c r="G248" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -6352,8 +7109,11 @@
       <c r="G249" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>21</v>
       </c>
@@ -6375,8 +7135,11 @@
       <c r="G250" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>45</v>
       </c>
@@ -6398,8 +7161,11 @@
       <c r="G251" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="8" t="s">
         <v>58</v>
       </c>
@@ -6421,8 +7187,11 @@
       <c r="G252" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>21</v>
       </c>
@@ -6444,8 +7213,11 @@
       <c r="G253" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>30</v>
       </c>
@@ -6467,8 +7239,11 @@
       <c r="G254" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="8" t="s">
         <v>26</v>
       </c>
@@ -6490,8 +7265,11 @@
       <c r="G255" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>45</v>
       </c>
@@ -6513,8 +7291,11 @@
       <c r="G256" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>12</v>
       </c>
@@ -6536,8 +7317,11 @@
       <c r="G257" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>25</v>
       </c>
@@ -6559,8 +7343,11 @@
       <c r="G258" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>55</v>
       </c>
@@ -6582,8 +7369,11 @@
       <c r="G259" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>17</v>
       </c>
@@ -6605,8 +7395,11 @@
       <c r="G260" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="8" t="s">
         <v>58</v>
       </c>
@@ -6628,8 +7421,11 @@
       <c r="G261" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -6651,8 +7447,11 @@
       <c r="G262" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="8" t="s">
         <v>34</v>
       </c>
@@ -6674,8 +7473,11 @@
       <c r="G263" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>21</v>
       </c>
@@ -6697,8 +7499,11 @@
       <c r="G264" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="8" t="s">
         <v>26</v>
       </c>
@@ -6720,8 +7525,11 @@
       <c r="G265" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>45</v>
       </c>
@@ -6743,8 +7551,11 @@
       <c r="G266" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>25</v>
       </c>
@@ -6766,8 +7577,11 @@
       <c r="G267" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>37</v>
       </c>
@@ -6789,8 +7603,11 @@
       <c r="G268" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>44</v>
       </c>
@@ -6812,8 +7629,11 @@
       <c r="G269" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>17</v>
       </c>
@@ -6835,8 +7655,11 @@
       <c r="G270" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="8" t="s">
         <v>58</v>
       </c>
@@ -6858,8 +7681,11 @@
       <c r="G271" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>21</v>
       </c>
@@ -6881,8 +7707,11 @@
       <c r="G272" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>30</v>
       </c>
@@ -6904,8 +7733,11 @@
       <c r="G273" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="8" t="s">
         <v>26</v>
       </c>
@@ -6927,8 +7759,11 @@
       <c r="G274" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>45</v>
       </c>
@@ -6950,8 +7785,11 @@
       <c r="G275" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>57</v>
       </c>
@@ -6973,8 +7811,11 @@
       <c r="G276" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>54</v>
       </c>
@@ -6996,8 +7837,11 @@
       <c r="G277" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>17</v>
       </c>
@@ -7019,8 +7863,11 @@
       <c r="G278" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="8" t="s">
         <v>58</v>
       </c>
@@ -7042,8 +7889,11 @@
       <c r="G279" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="8" t="s">
         <v>50</v>
       </c>
@@ -7065,8 +7915,11 @@
       <c r="G280" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>51</v>
       </c>
@@ -7088,8 +7941,11 @@
       <c r="G281" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>21</v>
       </c>
@@ -7111,8 +7967,11 @@
       <c r="G282" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>30</v>
       </c>
@@ -7134,8 +7993,11 @@
       <c r="G283" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="8" t="s">
         <v>26</v>
       </c>
@@ -7157,8 +8019,11 @@
       <c r="G284" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>46</v>
       </c>
@@ -7180,8 +8045,11 @@
       <c r="G285" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>45</v>
       </c>
@@ -7203,8 +8071,11 @@
       <c r="G286" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>54</v>
       </c>
@@ -7226,8 +8097,11 @@
       <c r="G287" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>39</v>
       </c>
@@ -7249,8 +8123,11 @@
       <c r="G288" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>17</v>
       </c>
@@ -7272,8 +8149,11 @@
       <c r="G289" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="8" t="s">
         <v>58</v>
       </c>
@@ -7295,8 +8175,11 @@
       <c r="G290" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>44</v>
       </c>
@@ -7318,8 +8201,11 @@
       <c r="G291" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>44</v>
       </c>
@@ -7341,8 +8227,11 @@
       <c r="G292" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>21</v>
       </c>
@@ -7364,8 +8253,11 @@
       <c r="G293" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>36</v>
       </c>
@@ -7387,8 +8279,11 @@
       <c r="G294" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="8" t="s">
         <v>52</v>
       </c>
@@ -7410,8 +8305,11 @@
       <c r="G295" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="8" t="s">
         <v>26</v>
       </c>
@@ -7433,8 +8331,11 @@
       <c r="G296" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>45</v>
       </c>
@@ -7456,8 +8357,11 @@
       <c r="G297" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>29</v>
       </c>
@@ -7479,8 +8383,11 @@
       <c r="G298" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>54</v>
       </c>
@@ -7502,8 +8409,11 @@
       <c r="G299" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>17</v>
       </c>
@@ -7525,8 +8435,11 @@
       <c r="G300" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="8" t="s">
         <v>58</v>
       </c>
@@ -7548,8 +8461,11 @@
       <c r="G301" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="8" t="s">
         <v>38</v>
       </c>
@@ -7571,8 +8487,11 @@
       <c r="G302" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="8" t="s">
         <v>50</v>
       </c>
@@ -7594,8 +8513,11 @@
       <c r="G303" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>13</v>
       </c>
@@ -7617,8 +8539,11 @@
       <c r="G304" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>21</v>
       </c>
@@ -7640,8 +8565,11 @@
       <c r="G305" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>17</v>
       </c>
@@ -7663,8 +8591,11 @@
       <c r="G306" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -7686,8 +8617,11 @@
       <c r="G307" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="8" t="s">
         <v>58</v>
       </c>
@@ -7709,8 +8643,11 @@
       <c r="G308" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="8" t="s">
         <v>26</v>
       </c>
@@ -7732,8 +8669,11 @@
       <c r="G309" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>45</v>
       </c>
@@ -7755,8 +8695,11 @@
       <c r="G310" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>45</v>
       </c>
@@ -7778,8 +8721,11 @@
       <c r="G311" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>21</v>
       </c>
@@ -7801,8 +8747,11 @@
       <c r="G312" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>54</v>
       </c>
@@ -7824,8 +8773,11 @@
       <c r="G313" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="8" t="s">
         <v>26</v>
       </c>
@@ -7847,8 +8799,11 @@
       <c r="G314" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="8" t="s">
         <v>48</v>
       </c>
@@ -7870,8 +8825,11 @@
       <c r="G315" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>17</v>
       </c>
@@ -7893,8 +8851,11 @@
       <c r="G316" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="8" t="s">
         <v>58</v>
       </c>
@@ -7916,8 +8877,11 @@
       <c r="G317" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>21</v>
       </c>
@@ -7939,8 +8903,11 @@
       <c r="G318" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="8" t="s">
         <v>48</v>
       </c>
@@ -7962,8 +8929,11 @@
       <c r="G319" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>49</v>
       </c>
@@ -7985,8 +8955,11 @@
       <c r="G320" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="8" t="s">
         <v>26</v>
       </c>
@@ -8008,8 +8981,11 @@
       <c r="G321" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>45</v>
       </c>
@@ -8031,8 +9007,11 @@
       <c r="G322" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>12</v>
       </c>
@@ -8054,8 +9033,11 @@
       <c r="G323" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>25</v>
       </c>
@@ -8077,8 +9059,11 @@
       <c r="G324" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>42</v>
       </c>
@@ -8100,8 +9085,11 @@
       <c r="G325" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>17</v>
       </c>
@@ -8123,8 +9111,11 @@
       <c r="G326" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="8" t="s">
         <v>58</v>
       </c>
@@ -8146,8 +9137,11 @@
       <c r="G327" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>10</v>
       </c>
@@ -8169,8 +9163,11 @@
       <c r="G328" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>51</v>
       </c>
@@ -8192,8 +9189,11 @@
       <c r="G329" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>21</v>
       </c>
@@ -8215,8 +9215,11 @@
       <c r="G330" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="8" t="s">
         <v>26</v>
       </c>
@@ -8238,8 +9241,11 @@
       <c r="G331" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>45</v>
       </c>
@@ -8261,8 +9267,11 @@
       <c r="G332" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>54</v>
       </c>
@@ -8284,8 +9293,11 @@
       <c r="G333" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="8" t="s">
         <v>47</v>
       </c>
@@ -8307,8 +9319,11 @@
       <c r="G334" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>39</v>
       </c>
@@ -8330,8 +9345,11 @@
       <c r="G335" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>44</v>
       </c>
@@ -8353,8 +9371,11 @@
       <c r="G336" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>17</v>
       </c>
@@ -8376,8 +9397,11 @@
       <c r="G337" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="8" t="s">
         <v>58</v>
       </c>
@@ -8399,8 +9423,11 @@
       <c r="G338" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>21</v>
       </c>
@@ -8422,8 +9449,11 @@
       <c r="G339" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>15</v>
       </c>
@@ -8445,8 +9475,11 @@
       <c r="G340" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="8" t="s">
         <v>26</v>
       </c>
@@ -8468,8 +9501,11 @@
       <c r="G341" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>45</v>
       </c>
@@ -8491,8 +9527,11 @@
       <c r="G342" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>12</v>
       </c>
@@ -8514,8 +9553,11 @@
       <c r="G343" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>29</v>
       </c>
@@ -8537,8 +9579,11 @@
       <c r="G344" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>54</v>
       </c>
@@ -8560,8 +9605,11 @@
       <c r="G345" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>39</v>
       </c>
@@ -8583,8 +9631,11 @@
       <c r="G346" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>55</v>
       </c>
@@ -8606,8 +9657,11 @@
       <c r="G347" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>37</v>
       </c>
@@ -8629,8 +9683,11 @@
       <c r="G348" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>17</v>
       </c>
@@ -8652,8 +9709,11 @@
       <c r="G349" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="8" t="s">
         <v>58</v>
       </c>
@@ -8675,8 +9735,11 @@
       <c r="G350" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>10</v>
       </c>
@@ -8698,8 +9761,11 @@
       <c r="G351" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>21</v>
       </c>
@@ -8721,8 +9787,11 @@
       <c r="G352" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>36</v>
       </c>
@@ -8744,8 +9813,11 @@
       <c r="G353" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="8" t="s">
         <v>26</v>
       </c>
@@ -8767,8 +9839,11 @@
       <c r="G354" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>45</v>
       </c>
@@ -8790,8 +9865,11 @@
       <c r="G355" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>12</v>
       </c>
@@ -8813,8 +9891,11 @@
       <c r="G356" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>29</v>
       </c>
@@ -8836,8 +9917,11 @@
       <c r="G357" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>27</v>
       </c>
@@ -8859,8 +9943,11 @@
       <c r="G358" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>39</v>
       </c>
@@ -8882,8 +9969,11 @@
       <c r="G359" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>37</v>
       </c>
@@ -8905,8 +9995,11 @@
       <c r="G360" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>17</v>
       </c>
@@ -8928,8 +10021,11 @@
       <c r="G361" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="8" t="s">
         <v>58</v>
       </c>
@@ -8951,8 +10047,11 @@
       <c r="G362" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>10</v>
       </c>
@@ -8974,8 +10073,11 @@
       <c r="G363" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>51</v>
       </c>
@@ -8997,8 +10099,11 @@
       <c r="G364" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>21</v>
       </c>
@@ -9020,8 +10125,11 @@
       <c r="G365" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="8" t="s">
         <v>26</v>
       </c>
@@ -9043,8 +10151,11 @@
       <c r="G366" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>45</v>
       </c>
@@ -9066,8 +10177,11 @@
       <c r="G367" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>54</v>
       </c>
@@ -9089,8 +10203,11 @@
       <c r="G368" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>39</v>
       </c>
@@ -9112,8 +10229,11 @@
       <c r="G369" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>17</v>
       </c>
@@ -9135,8 +10255,11 @@
       <c r="G370" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>35</v>
       </c>
@@ -9158,8 +10281,11 @@
       <c r="G371" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="8" t="s">
         <v>58</v>
       </c>
@@ -9181,8 +10307,11 @@
       <c r="G372" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>21</v>
       </c>
@@ -9204,8 +10333,11 @@
       <c r="G373" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="8" t="s">
         <v>26</v>
       </c>
@@ -9227,8 +10359,11 @@
       <c r="G374" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>45</v>
       </c>
@@ -9250,8 +10385,11 @@
       <c r="G375" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>54</v>
       </c>
@@ -9273,8 +10411,11 @@
       <c r="G376" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>33</v>
       </c>
@@ -9296,8 +10437,11 @@
       <c r="G377" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="8" t="s">
         <v>47</v>
       </c>
@@ -9319,8 +10463,11 @@
       <c r="G378" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>42</v>
       </c>
@@ -9342,8 +10489,11 @@
       <c r="G379" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>17</v>
       </c>
@@ -9365,8 +10515,11 @@
       <c r="G380" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="8" t="s">
         <v>58</v>
       </c>
@@ -9388,8 +10541,11 @@
       <c r="G381" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>10</v>
       </c>
@@ -9411,8 +10567,11 @@
       <c r="G382" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="8" t="s">
         <v>53</v>
       </c>
@@ -9434,8 +10593,11 @@
       <c r="G383" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="8" t="s">
         <v>34</v>
       </c>
@@ -9457,9 +10619,12 @@
       <c r="G384" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A385" s="8" t="s">
+      <c r="H384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A385" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B385" s="1" t="s">
@@ -9480,8 +10645,11 @@
       <c r="G385" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>21</v>
       </c>
@@ -9503,8 +10671,11 @@
       <c r="G386" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>49</v>
       </c>
@@ -9526,8 +10697,11 @@
       <c r="G387" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="8" t="s">
         <v>26</v>
       </c>
@@ -9549,8 +10723,11 @@
       <c r="G388" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>41</v>
       </c>
@@ -9572,8 +10749,11 @@
       <c r="G389" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>45</v>
       </c>
@@ -9595,8 +10775,11 @@
       <c r="G390" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>12</v>
       </c>
@@ -9618,8 +10801,11 @@
       <c r="G391" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>28</v>
       </c>
@@ -9641,8 +10827,11 @@
       <c r="G392" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>54</v>
       </c>
@@ -9664,8 +10853,11 @@
       <c r="G393" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>33</v>
       </c>
@@ -9687,8 +10879,11 @@
       <c r="G394" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>17</v>
       </c>
@@ -9710,8 +10905,11 @@
       <c r="G395" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="8" t="s">
         <v>58</v>
       </c>
@@ -9733,8 +10931,11 @@
       <c r="G396" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="8" t="s">
         <v>53</v>
       </c>
@@ -9756,8 +10957,11 @@
       <c r="G397" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="8" t="s">
         <v>34</v>
       </c>
@@ -9779,8 +10983,11 @@
       <c r="G398" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="7" t="s">
         <v>22</v>
       </c>
@@ -9802,8 +11009,11 @@
       <c r="G399" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="8" t="s">
         <v>34</v>
       </c>
@@ -9825,8 +11035,11 @@
       <c r="G400" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="8" t="s">
         <v>34</v>
       </c>
@@ -9848,8 +11061,11 @@
       <c r="G401" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>21</v>
       </c>
@@ -9871,8 +11087,11 @@
       <c r="G402" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>30</v>
       </c>
@@ -9894,8 +11113,11 @@
       <c r="G403" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="8" t="s">
         <v>52</v>
       </c>
@@ -9917,8 +11139,11 @@
       <c r="G404" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="8" t="s">
         <v>26</v>
       </c>
@@ -9940,8 +11165,11 @@
       <c r="G405" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>45</v>
       </c>
@@ -9963,8 +11191,11 @@
       <c r="G406" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>13</v>
       </c>
@@ -9986,8 +11217,11 @@
       <c r="G407" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>54</v>
       </c>
@@ -10009,8 +11243,11 @@
       <c r="G408" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>42</v>
       </c>
@@ -10032,8 +11269,11 @@
       <c r="G409" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>17</v>
       </c>
@@ -10055,8 +11295,11 @@
       <c r="G410" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="8" t="s">
         <v>58</v>
       </c>
@@ -10078,8 +11321,11 @@
       <c r="G411" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="8" t="s">
         <v>40</v>
       </c>
@@ -10101,8 +11347,11 @@
       <c r="G412" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="7" t="s">
         <v>22</v>
       </c>
@@ -10124,8 +11373,11 @@
       <c r="G413" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="8" t="s">
         <v>50</v>
       </c>
@@ -10147,8 +11399,11 @@
       <c r="G414" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>51</v>
       </c>
@@ -10170,8 +11425,11 @@
       <c r="G415" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>21</v>
       </c>
@@ -10193,8 +11451,11 @@
       <c r="G416" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>30</v>
       </c>
@@ -10216,8 +11477,11 @@
       <c r="G417" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="8" t="s">
         <v>26</v>
       </c>
@@ -10239,8 +11503,11 @@
       <c r="G418" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>45</v>
       </c>
@@ -10262,8 +11529,11 @@
       <c r="G419" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>13</v>
       </c>
@@ -10285,8 +11555,11 @@
       <c r="G420" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>27</v>
       </c>
@@ -10308,8 +11581,11 @@
       <c r="G421" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>42</v>
       </c>
@@ -10331,8 +11607,11 @@
       <c r="G422" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>37</v>
       </c>
@@ -10354,8 +11633,11 @@
       <c r="G423" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>44</v>
       </c>
@@ -10377,8 +11659,11 @@
       <c r="G424" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>17</v>
       </c>
@@ -10400,8 +11685,11 @@
       <c r="G425" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="8" t="s">
         <v>58</v>
       </c>
@@ -10423,8 +11711,11 @@
       <c r="G426" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="8" t="s">
         <v>40</v>
       </c>
@@ -10446,8 +11737,11 @@
       <c r="G427" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="8" t="s">
         <v>34</v>
       </c>
@@ -10469,8 +11763,11 @@
       <c r="G428" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H428">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="8" t="s">
         <v>50</v>
       </c>
@@ -10492,8 +11789,11 @@
       <c r="G429" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H429">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>21</v>
       </c>
@@ -10515,8 +11815,11 @@
       <c r="G430" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>30</v>
       </c>
@@ -10538,8 +11841,11 @@
       <c r="G431" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>16</v>
       </c>
@@ -10561,8 +11867,11 @@
       <c r="G432" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="8" t="s">
         <v>52</v>
       </c>
@@ -10584,8 +11893,11 @@
       <c r="G433" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="8" t="s">
         <v>26</v>
       </c>
@@ -10607,8 +11919,11 @@
       <c r="G434" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>45</v>
       </c>
@@ -10630,8 +11945,11 @@
       <c r="G435" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>13</v>
       </c>
@@ -10653,8 +11971,11 @@
       <c r="G436" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>54</v>
       </c>
@@ -10676,8 +11997,11 @@
       <c r="G437" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>27</v>
       </c>
@@ -10699,8 +12023,11 @@
       <c r="G438" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>39</v>
       </c>
@@ -10722,8 +12049,11 @@
       <c r="G439" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>55</v>
       </c>
@@ -10745,8 +12075,11 @@
       <c r="G440" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>42</v>
       </c>
@@ -10768,8 +12101,11 @@
       <c r="G441" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>44</v>
       </c>
@@ -10791,8 +12127,11 @@
       <c r="G442" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>17</v>
       </c>
@@ -10814,8 +12153,11 @@
       <c r="G443" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>20</v>
       </c>
@@ -10837,8 +12179,11 @@
       <c r="G444" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="8" t="s">
         <v>58</v>
       </c>
@@ -10860,8 +12205,11 @@
       <c r="G445" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="8" t="s">
         <v>40</v>
       </c>
@@ -10883,8 +12231,11 @@
       <c r="G446" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="8" t="s">
         <v>50</v>
       </c>
@@ -10906,8 +12257,11 @@
       <c r="G447" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>21</v>
       </c>
@@ -10929,8 +12283,11 @@
       <c r="G448" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>30</v>
       </c>
@@ -10952,8 +12309,11 @@
       <c r="G449" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="8" t="s">
         <v>26</v>
       </c>
@@ -10975,8 +12335,11 @@
       <c r="G450" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>45</v>
       </c>
@@ -10998,8 +12361,11 @@
       <c r="G451" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>28</v>
       </c>
@@ -11021,8 +12387,11 @@
       <c r="G452" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>55</v>
       </c>
@@ -11044,8 +12413,11 @@
       <c r="G453" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>17</v>
       </c>
@@ -11067,8 +12439,11 @@
       <c r="G454" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="8" t="s">
         <v>58</v>
       </c>
@@ -11090,8 +12465,11 @@
       <c r="G455" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="8" t="s">
         <v>34</v>
       </c>
@@ -11113,8 +12491,11 @@
       <c r="G456" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="8" t="s">
         <v>38</v>
       </c>
@@ -11136,8 +12517,11 @@
       <c r="G457" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="8" t="s">
         <v>50</v>
       </c>
@@ -11159,8 +12543,11 @@
       <c r="G458" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>21</v>
       </c>
@@ -11182,8 +12569,11 @@
       <c r="G459" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>30</v>
       </c>
@@ -11205,8 +12595,11 @@
       <c r="G460" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="8" t="s">
         <v>26</v>
       </c>
@@ -11228,8 +12621,11 @@
       <c r="G461" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>45</v>
       </c>
@@ -11251,8 +12647,11 @@
       <c r="G462" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="8" t="s">
         <v>47</v>
       </c>
@@ -11274,8 +12673,11 @@
       <c r="G463" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H463">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>55</v>
       </c>
@@ -11297,8 +12699,11 @@
       <c r="G464" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>17</v>
       </c>
@@ -11320,8 +12725,11 @@
       <c r="G465" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="8" t="s">
         <v>58</v>
       </c>
@@ -11343,8 +12751,11 @@
       <c r="G466" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="8" t="s">
         <v>38</v>
       </c>
@@ -11366,8 +12777,11 @@
       <c r="G467" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="7" t="s">
         <v>24</v>
       </c>
@@ -11389,8 +12803,11 @@
       <c r="G468" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="8" t="s">
         <v>50</v>
       </c>
@@ -11412,8 +12829,11 @@
       <c r="G469" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H469">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>21</v>
       </c>
@@ -11435,8 +12855,11 @@
       <c r="G470" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="8" t="s">
         <v>26</v>
       </c>
@@ -11458,8 +12881,11 @@
       <c r="G471" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H471">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>45</v>
       </c>
@@ -11481,8 +12907,11 @@
       <c r="G472" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>28</v>
       </c>
@@ -11504,8 +12933,11 @@
       <c r="G473" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="8" t="s">
         <v>47</v>
       </c>
@@ -11527,8 +12959,11 @@
       <c r="G474" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>55</v>
       </c>
@@ -11550,8 +12985,11 @@
       <c r="G475" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>32</v>
       </c>
@@ -11573,8 +13011,11 @@
       <c r="G476" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>37</v>
       </c>
@@ -11596,8 +13037,11 @@
       <c r="G477" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>44</v>
       </c>
@@ -11619,8 +13063,11 @@
       <c r="G478" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>17</v>
       </c>
@@ -11642,8 +13089,11 @@
       <c r="G479" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="8" t="s">
         <v>58</v>
       </c>
@@ -11665,8 +13115,11 @@
       <c r="G480" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="7" t="s">
         <v>22</v>
       </c>
@@ -11688,8 +13141,11 @@
       <c r="G481" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="7" t="s">
         <v>24</v>
       </c>
@@ -11711,8 +13167,11 @@
       <c r="G482" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="8" t="s">
         <v>50</v>
       </c>
@@ -11734,8 +13193,11 @@
       <c r="G483" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>51</v>
       </c>
@@ -11757,8 +13219,11 @@
       <c r="G484" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>21</v>
       </c>
@@ -11780,8 +13245,11 @@
       <c r="G485" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H485">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="8" t="s">
         <v>52</v>
       </c>
@@ -11803,8 +13271,11 @@
       <c r="G486" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="8" t="s">
         <v>26</v>
       </c>
@@ -11826,8 +13297,11 @@
       <c r="G487" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>45</v>
       </c>
@@ -11849,8 +13323,11 @@
       <c r="G488" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H488">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>17</v>
       </c>
@@ -11872,8 +13349,11 @@
       <c r="G489" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="8" t="s">
         <v>58</v>
       </c>
@@ -11895,8 +13375,11 @@
       <c r="G490" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="7" t="s">
         <v>24</v>
       </c>
@@ -11918,8 +13401,11 @@
       <c r="G491" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H491">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="8" t="s">
         <v>50</v>
       </c>
@@ -11941,8 +13427,11 @@
       <c r="G492" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>21</v>
       </c>
@@ -11964,8 +13453,11 @@
       <c r="G493" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="8" t="s">
         <v>52</v>
       </c>
@@ -11987,8 +13479,11 @@
       <c r="G494" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H494">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="8" t="s">
         <v>26</v>
       </c>
@@ -12010,8 +13505,11 @@
       <c r="G495" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>41</v>
       </c>
@@ -12033,8 +13531,11 @@
       <c r="G496" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H496">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
         <v>45</v>
       </c>
@@ -12056,8 +13557,11 @@
       <c r="G497" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H497">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
         <v>28</v>
       </c>
@@ -12079,8 +13583,11 @@
       <c r="G498" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H498">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
         <v>25</v>
       </c>
@@ -12102,8 +13609,11 @@
       <c r="G499" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H499">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
         <v>39</v>
       </c>
@@ -12125,8 +13635,11 @@
       <c r="G500" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H500">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
         <v>17</v>
       </c>
@@ -12148,8 +13661,11 @@
       <c r="G501" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H501">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
         <v>35</v>
       </c>
@@ -12171,8 +13687,11 @@
       <c r="G502" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="8" t="s">
         <v>58</v>
       </c>
@@ -12194,8 +13713,11 @@
       <c r="G503" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H503">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="8" t="s">
         <v>34</v>
       </c>
@@ -12217,8 +13739,11 @@
       <c r="G504" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A505" s="6" t="s">
         <v>18</v>
       </c>
@@ -12240,8 +13765,11 @@
       <c r="G505" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="8" t="s">
         <v>50</v>
       </c>
@@ -12263,8 +13791,11 @@
       <c r="G506" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
         <v>21</v>
       </c>
@@ -12286,8 +13817,11 @@
       <c r="G507" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
         <v>56</v>
       </c>
@@ -12309,8 +13843,11 @@
       <c r="G508" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="8" t="s">
         <v>52</v>
       </c>
@@ -12332,8 +13869,11 @@
       <c r="G509" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="8" t="s">
         <v>26</v>
       </c>
@@ -12355,8 +13895,11 @@
       <c r="G510" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>45</v>
       </c>
@@ -12378,8 +13921,11 @@
       <c r="G511" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>12</v>
       </c>
@@ -12401,8 +13947,11 @@
       <c r="G512" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H512">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>28</v>
       </c>
@@ -12424,8 +13973,11 @@
       <c r="G513" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H513">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>25</v>
       </c>
@@ -12447,8 +13999,11 @@
       <c r="G514" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H514">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>17</v>
       </c>
@@ -12470,8 +14025,11 @@
       <c r="G515" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H515">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="8" t="s">
         <v>58</v>
       </c>
@@ -12493,8 +14051,11 @@
       <c r="G516" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="8" t="s">
         <v>50</v>
       </c>
@@ -12516,8 +14077,11 @@
       <c r="G517" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>51</v>
       </c>
@@ -12539,8 +14103,11 @@
       <c r="G518" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>21</v>
       </c>
@@ -12562,8 +14129,11 @@
       <c r="G519" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H519">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>56</v>
       </c>
@@ -12585,8 +14155,11 @@
       <c r="G520" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H520">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="8" t="s">
         <v>52</v>
       </c>
@@ -12608,8 +14181,11 @@
       <c r="G521" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H521">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>49</v>
       </c>
@@ -12631,8 +14207,11 @@
       <c r="G522" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="8" t="s">
         <v>26</v>
       </c>
@@ -12654,8 +14233,11 @@
       <c r="G523" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H523">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>45</v>
       </c>
@@ -12677,8 +14259,11 @@
       <c r="G524" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>12</v>
       </c>
@@ -12700,8 +14285,11 @@
       <c r="G525" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>57</v>
       </c>
@@ -12723,8 +14311,11 @@
       <c r="G526" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>42</v>
       </c>
@@ -12746,8 +14337,11 @@
       <c r="G527" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>37</v>
       </c>
@@ -12769,8 +14363,11 @@
       <c r="G528" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>17</v>
       </c>
@@ -12792,8 +14389,11 @@
       <c r="G529" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="530" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>20</v>
       </c>
@@ -12815,8 +14415,11 @@
       <c r="G530" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="8" t="s">
         <v>58</v>
       </c>
@@ -12838,8 +14441,11 @@
       <c r="G531" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="532" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="9" t="s">
         <v>19</v>
       </c>
@@ -12861,8 +14467,11 @@
       <c r="G532" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="8" t="s">
         <v>50</v>
       </c>
@@ -12884,8 +14493,11 @@
       <c r="G533" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="534" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
         <v>21</v>
       </c>
@@ -12907,8 +14519,11 @@
       <c r="G534" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="535" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
         <v>30</v>
       </c>
@@ -12930,8 +14545,11 @@
       <c r="G535" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="536" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
         <v>15</v>
       </c>
@@ -12953,8 +14571,11 @@
       <c r="G536" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H536">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
         <v>49</v>
       </c>
@@ -12976,8 +14597,11 @@
       <c r="G537" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" s="8" t="s">
         <v>26</v>
       </c>
@@ -12999,8 +14623,11 @@
       <c r="G538" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H538">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
         <v>45</v>
       </c>
@@ -13022,8 +14649,11 @@
       <c r="G539" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="540" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H539">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
         <v>32</v>
       </c>
@@ -13045,8 +14675,11 @@
       <c r="G540" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
         <v>37</v>
       </c>
@@ -13068,8 +14701,11 @@
       <c r="G541" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="542" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
         <v>17</v>
       </c>
@@ -13091,8 +14727,11 @@
       <c r="G542" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H542">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="8" t="s">
         <v>58</v>
       </c>
@@ -13114,8 +14753,11 @@
       <c r="G543" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H543">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="8" t="s">
         <v>53</v>
       </c>
@@ -13137,8 +14779,11 @@
       <c r="G544" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H544">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="8" t="s">
         <v>34</v>
       </c>
@@ -13160,8 +14805,11 @@
       <c r="G545" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H545">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="8" t="s">
         <v>50</v>
       </c>
@@ -13183,8 +14831,11 @@
       <c r="G546" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H546">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="8" t="s">
         <v>34</v>
       </c>
@@ -13206,8 +14857,11 @@
       <c r="G547" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H547">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="8" t="s">
         <v>34</v>
       </c>
@@ -13229,8 +14883,11 @@
       <c r="G548" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H548">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>21</v>
       </c>
@@ -13252,8 +14909,11 @@
       <c r="G549" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="550" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H549">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>15</v>
       </c>
@@ -13275,8 +14935,11 @@
       <c r="G550" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H550">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>49</v>
       </c>
@@ -13298,8 +14961,11 @@
       <c r="G551" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H551">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="8" t="s">
         <v>26</v>
       </c>
@@ -13321,8 +14987,11 @@
       <c r="G552" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H552">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>45</v>
       </c>
@@ -13344,8 +15013,11 @@
       <c r="G553" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="554" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H553">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>32</v>
       </c>
@@ -13367,8 +15039,11 @@
       <c r="G554" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="555" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>17</v>
       </c>
@@ -13390,8 +15065,11 @@
       <c r="G555" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="556" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H555">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="8" t="s">
         <v>58</v>
       </c>
@@ -13413,8 +15091,11 @@
       <c r="G556" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="557" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H556">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="8" t="s">
         <v>40</v>
       </c>
@@ -13436,8 +15117,11 @@
       <c r="G557" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="558" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H557">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="7" t="s">
         <v>22</v>
       </c>
@@ -13459,8 +15143,11 @@
       <c r="G558" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="559" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H558">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="8" t="s">
         <v>50</v>
       </c>
@@ -13482,8 +15169,11 @@
       <c r="G559" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="560" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H559">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="8" t="s">
         <v>50</v>
       </c>
@@ -13505,8 +15195,11 @@
       <c r="G560" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="561" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H560">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>51</v>
       </c>
@@ -13528,8 +15221,11 @@
       <c r="G561" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="562" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>51</v>
       </c>
@@ -13551,8 +15247,11 @@
       <c r="G562" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="563" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H562">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>21</v>
       </c>
@@ -13574,8 +15273,11 @@
       <c r="G563" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="564" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>21</v>
       </c>
@@ -13597,8 +15299,11 @@
       <c r="G564" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="565" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H564">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>21</v>
       </c>
@@ -13620,8 +15325,11 @@
       <c r="G565" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="566" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H565">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>36</v>
       </c>
@@ -13643,8 +15351,11 @@
       <c r="G566" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="567" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H566">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="8" t="s">
         <v>52</v>
       </c>
@@ -13666,8 +15377,11 @@
       <c r="G567" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="568" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H567">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="8" t="s">
         <v>52</v>
       </c>
@@ -13689,8 +15403,11 @@
       <c r="G568" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="569" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H568">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>15</v>
       </c>
@@ -13712,8 +15429,11 @@
       <c r="G569" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="570" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H569">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>15</v>
       </c>
@@ -13735,8 +15455,11 @@
       <c r="G570" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H570">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>15</v>
       </c>
@@ -13758,8 +15481,11 @@
       <c r="G571" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="572" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H571">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="8" t="s">
         <v>26</v>
       </c>
@@ -13781,8 +15507,11 @@
       <c r="G572" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H572">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="8" t="s">
         <v>26</v>
       </c>
@@ -13804,8 +15533,11 @@
       <c r="G573" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="574" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H573">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="8" t="s">
         <v>26</v>
       </c>
@@ -13827,8 +15559,11 @@
       <c r="G574" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H574">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>31</v>
       </c>
@@ -13850,8 +15585,11 @@
       <c r="G575" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="576" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H575">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>45</v>
       </c>
@@ -13873,8 +15611,11 @@
       <c r="G576" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H576">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>45</v>
       </c>
@@ -13896,8 +15637,11 @@
       <c r="G577" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H577">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>45</v>
       </c>
@@ -13919,8 +15663,11 @@
       <c r="G578" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H578">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>12</v>
       </c>
@@ -13942,8 +15689,11 @@
       <c r="G579" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H579">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>13</v>
       </c>
@@ -13965,8 +15715,11 @@
       <c r="G580" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H580">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>29</v>
       </c>
@@ -13988,8 +15741,11 @@
       <c r="G581" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H581">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>27</v>
       </c>
@@ -14011,8 +15767,11 @@
       <c r="G582" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H582">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>27</v>
       </c>
@@ -14034,8 +15793,11 @@
       <c r="G583" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H583">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="8" t="s">
         <v>47</v>
       </c>
@@ -14057,8 +15819,11 @@
       <c r="G584" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H584">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="8" t="s">
         <v>47</v>
       </c>
@@ -14080,8 +15845,11 @@
       <c r="G585" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H585">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>55</v>
       </c>
@@ -14103,8 +15871,11 @@
       <c r="G586" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H586">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>55</v>
       </c>
@@ -14126,8 +15897,11 @@
       <c r="G587" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H587">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>32</v>
       </c>
@@ -14149,8 +15923,11 @@
       <c r="G588" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H588">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>37</v>
       </c>
@@ -14172,8 +15949,11 @@
       <c r="G589" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H589">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>44</v>
       </c>
@@ -14195,8 +15975,11 @@
       <c r="G590" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H590">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>44</v>
       </c>
@@ -14218,8 +16001,11 @@
       <c r="G591" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="592" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H591">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>17</v>
       </c>
@@ -14241,8 +16027,11 @@
       <c r="G592" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="593" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H592">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>17</v>
       </c>
@@ -14264,8 +16053,11 @@
       <c r="G593" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="594" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H593">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>17</v>
       </c>
@@ -14287,8 +16079,11 @@
       <c r="G594" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="595" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H594">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>35</v>
       </c>
@@ -14310,8 +16105,11 @@
       <c r="G595" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="596" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H595">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>20</v>
       </c>
@@ -14333,8 +16131,11 @@
       <c r="G596" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="597" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H596">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>20</v>
       </c>
@@ -14356,8 +16157,11 @@
       <c r="G597" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="598" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H597">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="8" t="s">
         <v>58</v>
       </c>
@@ -14379,8 +16183,11 @@
       <c r="G598" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="599" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H598">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="8" t="s">
         <v>58</v>
       </c>
@@ -14402,8 +16209,11 @@
       <c r="G599" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="600" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="8" t="s">
         <v>58</v>
       </c>
@@ -14425,8 +16235,11 @@
       <c r="G600" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="601" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H600">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>10</v>
       </c>
@@ -14448,8 +16261,11 @@
       <c r="G601" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="602" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H601">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="8" t="s">
         <v>40</v>
       </c>
@@ -14471,8 +16287,11 @@
       <c r="G602" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="603" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H602">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="8" t="s">
         <v>50</v>
       </c>
@@ -14494,8 +16313,11 @@
       <c r="G603" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="604" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H603">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="8" t="s">
         <v>50</v>
       </c>
@@ -14517,8 +16339,11 @@
       <c r="G604" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="605" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H604">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="8" t="s">
         <v>50</v>
       </c>
@@ -14539,13 +16364,21 @@
       </c>
       <c r="G605" t="s">
         <v>64</v>
+      </c>
+      <c r="H605">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G605">
     <filterColumn colId="0">
       <filters>
-        <filter val="vignesh.suryadevara@datafactz.com"/>
+        <filter val="bhargav.mekala@datafactz.com"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Yes"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -14562,8 +16395,10 @@
     <hyperlink ref="A165" r:id="rId2"/>
     <hyperlink ref="A197" r:id="rId3"/>
     <hyperlink ref="A505" r:id="rId4"/>
+    <hyperlink ref="A17" r:id="rId5"/>
+    <hyperlink ref="A385" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>